--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/31_Closing_Checkliste_Stand_22-10-2026.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/31_Closing_Checkliste_Stand_22-10-2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bedingungen" sheetId="1" r:id="R9460b2ad97da4fec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP_Uebergabe" sheetId="2" r:id="Rcc71404ee0bc4675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="3" r:id="R08f6be2efe374fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bedingungen" sheetId="1" r:id="Rb24a6461311540a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP_Uebergabe" sheetId="2" r:id="R2471e6ac3aa84701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="3" r:id="Rbc59928b602d4e3d"/>
   </x:sheets>
 </x:workbook>
 </file>
